--- a/corpus/xlsx/level-068/template.xlsx
+++ b/corpus/xlsx/level-068/template.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="24">
   <si>
     <r>
       <rPr>
@@ -119,7 +119,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -160,14 +168,6 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">e</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
     </r>
     <r>
       <rPr>
@@ -193,7 +193,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -209,15 +217,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">u</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">st</t>
+      <t xml:space="preserve">us</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">t</t>
     </r>
     <r>
       <rPr>
@@ -249,15 +257,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">r</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">r}</t>
     </r>
   </si>
   <si>
@@ -275,7 +275,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -316,14 +324,6 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
     </r>
     <r>
       <rPr>
@@ -349,7 +349,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -398,14 +406,6 @@
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">d</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
     </r>
     <r>
       <rPr>
@@ -431,7 +431,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -487,15 +495,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">d</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">d}</t>
     </r>
   </si>
   <si>
@@ -513,7 +513,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
+      <t xml:space="preserve">d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.</t>
     </r>
     <r>
       <rPr>
@@ -569,15 +577,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">l</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">l}</t>
     </r>
   </si>
   <si>
@@ -771,39 +771,31 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">#e</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">ac</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">h i</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">te</t>
+      <t xml:space="preserve">{</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">it</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">e</t>
     </r>
     <r>
       <rPr>
@@ -819,15 +811,23 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">}}{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{n</t>
+      <t xml:space="preserve">[i</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.n</t>
     </r>
     <r>
       <rPr>
@@ -843,7 +843,7 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">e}}</t>
+      <t xml:space="preserve">e}</t>
     </r>
   </si>
   <si>
@@ -853,31 +853,55 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">q</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">u</t>
+      <t xml:space="preserve">{d</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.i</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">te</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">ms</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">[i</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">].</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">qu</t>
     </r>
     <r>
       <rPr>
@@ -893,39 +917,15 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">i</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">t</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">y</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}}</t>
+      <t xml:space="preserve">ti</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">ty}</t>
     </r>
   </si>
   <si>
@@ -943,6 +943,80 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
+      <t xml:space="preserve">d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">it</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">em</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">s[</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">i</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">].</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">pr</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">ic</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">e}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
       <t xml:space="preserve">{</t>
     </r>
     <r>
@@ -951,55 +1025,71 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">p</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">r</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">i</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">c</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">e</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">}</t>
+      <t xml:space="preserve">d.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">it</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">em</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">s[</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">i+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">1]</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">.n</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">am</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">e}</t>
     </r>
   </si>
   <si>
@@ -1799,7 +1889,7 @@
     <xdr:ext cx="914400" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1" descr="{{image:red}}"/>
+        <xdr:cNvPr id="1" name="Picture 1" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1830,7 +1920,7 @@
     <xdr:ext cx="960120" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="2" name="Picture 2" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1861,7 +1951,7 @@
     <xdr:ext cx="1005840" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 3" descr="{{image:red}}"/>
+        <xdr:cNvPr id="3" name="Picture 3" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1892,7 +1982,7 @@
     <xdr:ext cx="1051560" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 4" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="4" name="Picture 4" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1923,7 +2013,7 @@
     <xdr:ext cx="1097280" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 5" descr="{{image:red}}"/>
+        <xdr:cNvPr id="5" name="Picture 5" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1954,7 +2044,7 @@
     <xdr:ext cx="1143000" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 6" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="6" name="Picture 6" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -1985,7 +2075,7 @@
     <xdr:ext cx="1188720" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 7" descr="{{image:red}}"/>
+        <xdr:cNvPr id="7" name="Picture 7" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2016,7 +2106,7 @@
     <xdr:ext cx="1234440" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 8" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="8" name="Picture 8" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2047,7 +2137,7 @@
     <xdr:ext cx="1280160" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 9" descr="{{image:red}}"/>
+        <xdr:cNvPr id="9" name="Picture 9" descr="{d.red}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2078,7 +2168,7 @@
     <xdr:ext cx="1325880" cy="609600"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Picture 10" descr="{{image:blue}}"/>
+        <xdr:cNvPr id="10" name="Picture 10" descr="{d.blue}"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -2104,7 +2194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -2431,10 +2521,10 @@
         <f>B40*C40</f>
         <v>0</v>
       </c>
-      <c r="E40" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{{/each}}</t>
-        </is>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -2461,7 +2551,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2485,7 +2575,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2509,7 +2599,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2533,7 +2623,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2557,7 +2647,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2581,7 +2671,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2605,7 +2695,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2629,7 +2719,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
@@ -2653,7 +2743,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="0">
         <v>7</v>
